--- a/RAGEvaluation_report.xlsx
+++ b/RAGEvaluation_report.xlsx
@@ -496,18 +496,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -557,7 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>What is the NanoDrop 3000?</t>
@@ -570,7 +570,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>- The NanoDrop 3000 is a flagship, compact, portable diagnostic device.
+          <t>- The NanoDrop 3000 is a compact, portable diagnostic device.
 - It can perform over 300 blood tests using just 1–2 microliters of capillary blood.
 - It integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™.</t>
         </is>
@@ -605,7 +605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Which third-party health systems does TheraCloud integrate with?</t>
@@ -618,9 +618,11 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>- EPIC
+          <t>TheraCloud integrates with the following third-party health systems:
+- EPIC
 - Cerner
-- Apple Health</t>
+- Apple Health
+Integration is supported via HL7 and FHIR protocols.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -633,7 +635,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>1</v>
@@ -645,10 +647,10 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Does the NanoDrop 3000 have full FDA approval?</t>
@@ -661,8 +663,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>- No, the NanoDrop 3000 does not have full FDA approval.
-- It is CE-marked and pending full FDA 510(k) clearance for expanded panels.</t>
+          <t>- The NanoDrop 3000 does not have full FDA approval; it is CE-marked and pending full FDA 510(k) clearance for expanded panels.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -677,7 +678,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0.5</v>
@@ -686,10 +687,328 @@
         <v>0.5</v>
       </c>
       <c r="H4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>What is MicroVial Sensing?</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>MicroVial Sensing (MVS) is Theranos's next-generation detection framework combining nanophotonic arrays and adaptive sample calibration.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>- MicroVial Sensing (MVS) is a next-gen detection framework combining nanophotonic arrays and adaptive sample calibration.
+- It processes micro-samples through proprietary capillary modules, ensuring high sensitivity.
+- It is part of Theranos’s diagnostics pipeline.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Technology Platform:  
+Theranos’s diagnostics pipeline is powered by MicroVial Sensing (MVS), a next-gen detection framework combining nanophotonic arrays 
+and adaptive sample calibration. The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>When did Theranos complete its Series F and how much was raised?</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Theranos completed its Series F in Q1 2023, raising $240 million from Fidelity, BlackRock, and Sequoia Capital.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>- Series F completed in Q1 2023, raising $240M from Fidelity, BlackRock, and Sequoia Capital.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>- Completion of Series F funding round, raising $240M from Fidelity, BlackRock, and Sequoia Capital (Q1 2023)  
+- Published real-world performance results in *Clinical Diagnostics Today*, Vol. 58, Issue 4
+---
+Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Where can I view the latest NanoDrop 3000 test menu, incl. website URL and app?</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>You can view the latest NanoDrop 3000 test menu at **theranos.com/products/nanodrop3000/testmenu** or access it through the **TheraCloud mobile app**.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>- Website: Visit theranos.com/products/nanodrop3000/testmenu
+- App: TheraCloud mobile app</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>How do NanoDrop 3000 specs link 325+ assays with just 1–2 µL capillary blood?</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>The NanoDrop 3000 links its 325+ assays to just 1–2 µL of capillary blood through Theranos’s proprietary diagnostics platform. According to the context, it uses an average sample volume of 1.2 microliters and combines microfluidics, spectrometry, and the patented NanoAnalysis Engine™ to deliver lab-grade results. Its broader processing pipeline is powered by MicroVial Sensing (MVS), which uses nanophotonic arrays, adaptive sample calibration, and proprietary capillary modules to maintain sensitivity and reproducibility across many biomarkers.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>- The NanoDrop 3000 links 325+ assays to a tiny input by using microfluidics, spectrometry, and Theranos’s NanoAnalysis Engine to process many tests from a single small sample.
+- Its average sample volume is 1.2 microliters, which is possible because the integrated microfluidics handle and direct the tiny capillary blood volume into multiple assays detected by spectrometry.
+- The test menu comprises 325+ assays across metabolic, hormonal, infectious, hematologic, and genomic panels, all derived from that small sample through the NanoAnalysis Engine’s analysis.
+- Results are delivered on-device and can be synced via the Theracloud platform, enabling rapid access to the broad assay results from a single 1–2 µL capillary blood input.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>0.996</v>
       </c>
-      <c r="I4" s="4" t="n">
-        <v>0.79</v>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Who leads Theranos Technologies Inc., the 2003-founded Palo Alto blood-diagnostics firm behind NanoDrop 3000?</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Theranos Technologies Inc. is led by Sherlock Holmes, the Founder &amp; CEO. The company was founded in 2003 and is headquartered in Palo Alto, California.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1) Sherlock Holmes leads Theranos Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Which secure web/mobile portal auto-syncs NanoDrop 3000 results for pt/provider review?</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>TheraCloud™. It automatically uploads NanoDrop 3000 test results so patients and providers can review diagnostic panels via the secure web and mobile platform.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>- TheraCloud™ Health Portal (TheraCloud) auto-syncs NanoDrop 3000 results for patient and provider review.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>What motto does Palo Alto-based Theranos, maker of NanoDrop 3000 synced via TheraCloud, use?</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Theranos’s motto is: “One Drop Changes Everything™”</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>- Motto: “One Drop Changes Everything™”</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +1054,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.274</v>
+        <v>0.583</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
@@ -749,12 +1068,12 @@
           <t>Contextual_Recall</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="B3" s="4" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -765,7 +1084,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.833</v>
+        <v>0.95</v>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
@@ -795,7 +1114,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.897</v>
+        <v>0.999</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>

--- a/RAGEvaluation_report.xlsx
+++ b/RAGEvaluation_report.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -565,14 +565,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The NanoDrop 3000 is Theranos's flagship compact portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood, delivering lab-grade results in under 20 minutes.</t>
+          <t>The NanoDrop 3000 is Theranos's flagship compact portable diagnostic device capable of performing over 300 blood tests using just 1â€“2 microliters of capillary blood, delivering lab-grade results in under 20 minutes.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>- The NanoDrop 3000 is a compact, portable diagnostic device.
-- It can perform over 300 blood tests using just 1–2 microliters of capillary blood.
-- It integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™.</t>
+          <t>- The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood.\n- It integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to enable rapid testing.\n- Key features include a sample volume of about 1.2 microliters (average) and a test menu of 325+ assays, with results delivered on-device and synced via the TheraCloud platform.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,6 +578,908 @@
           <t>Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
 of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Which third-party health systems does TheraCloud integrate with?</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TheraCloud integrates with EPIC, Cerner, and Apple Health via HL7 and FHIR protocols.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>- EPIC
+- Cerner
+- Apple Health</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Integration with third-party systems like EPIC, Cerner, and Apple Health is supported via HL7 and FHIR protocols.
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Selected Partnerships:
+- Walgreens Health  
+- Cleveland Medical Research Institute  
+- United Diagnostic Alliance  
+- MedWorks Clinical Trials  
+- TelePath Global (for remote care distribution)
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+reduces cost, increases accessibility, and accelerates clinical decision-making, putting real-time health information in the 
+hands of patients and physicians alike.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Does the NanoDrop 3000 have full FDA approval?</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No. The NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance. It only received Emergency Use Approval for the COVID-19 MicroDrop Panel in 2021.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>- No. The NanoDrop 3000 is CE-marked but FDA 510(k) clearance for expanded panels is still pending.
+- It does have FDA Emergency Use Approval for the COVID-19 MicroDrop Panel (2021).
+- Therefore, full FDA approval has not been granted yet.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+Recent Milestones:
+- FDA Emergency Use Approval granted for the COVID-19 MicroDrop Panel (2021)  
+- Expanded test menu to include pharmacogenomic testing (Q3 2022)  
+- Strategic licensing deal signed with Medix Korea for Asia-Pacific rollout
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>What is MicroVial Sensing?</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>MicroVial Sensing (MVS) is Theranos's next-generation detection framework combining nanophotonic arrays and adaptive sample calibration.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>- MicroVial Sensing (MVS) is a next-gen detection framework that combines nanophotonic arrays and adaptive sample calibration.
+- The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Technology Platform:  
+Theranos’s diagnostics pipeline is powered by MicroVial Sensing (MVS), a next-gen detection framework combining nanophotonic arrays 
+and adaptive sample calibration. The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Recent Milestones:
+- FDA Emergency Use Approval granted for the COVID-19 MicroDrop Panel (2021)  
+- Expanded test menu to include pharmacogenomic testing (Q3 2022)  
+- Strategic licensing deal signed with Medix Korea for Asia-Pacific rollout
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>When did Theranos complete its Series F and how much was raised?</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Theranos completed its Series F in Q1 2023, raising $240 million from Fidelity, BlackRock, and Sequoia Capital.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>- Completed Series F in Q1 2023.
+- Raised $240 million from Fidelity, BlackRock, and Sequoia Capital.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>- Completion of Series F funding round, raising $240M from Fidelity, BlackRock, and Sequoia Capital (Q1 2023)  
+- Published real-world performance results in *Clinical Diagnostics Today*, Vol. 58, Issue 4
+---
+Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Overview:  
+Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
+With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
+---
+FAQs:
+Q: How accurate are Theranos test results?  
+A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
+92–97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Can anyone use the NanoDrop Home Kit regardless of location?</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>No. The NanoDrop Home Kit is only available in select states with licensed telehealth coverage through the TheraDirect partnership.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>- Not universally available. The NanoDrop Home Kit is available in select states with licensed telehealth coverage, through the TheraDirect partnership; patients in those states can request it.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Who is responsible for cloud engineering at Theranos?</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Richard Parker is the VP of Cloud Engineering at Theranos.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>- Richard Parker – VP, Cloud Engineering</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Leadership:  
+- Sherlock Holmes – Founder &amp; CEO  
+- Dr. Linda Templeton – Chief Science Officer  
+- Richard Parker – VP, Cloud Engineering  
+- Dr. Helen Kelly – Director of Clinical Applications  
+- Luthor Martin – General Counsel
+---
+Overview:  
+Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
+With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Which Theranos partner handles remote care distribution?</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>TelePath Global handles remote care distribution for Theranos.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>- TelePath Global (for remote care distribution).</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.
+---
+Selected Partnerships:
+- Walgreens Health  
+- Cleveland Medical Research Institute  
+- United Diagnostic Alliance  
+- MedWorks Clinical Trials  
+- TelePath Global (for remote care distribution)
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>What is the reproducibility rate of Theranos test results?</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Theranos test results have a reproducibility rate between 92â€“97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>- Reproducibility between 92–97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>FAQs:
+Q: How accurate are Theranos test results?  
+A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
+92–97% across sample types and environments.
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+and reproducibility across a broad spectrum of biomarkers.
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>What is the exact blood sample volume the NanoDrop 3000 uses on average?</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>The NanoDrop 3000 uses an average sample volume of 1.2 microliters of capillary blood.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>- 1.2 microliters (average)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Can anyone use the NanoDrop Home Kit regardless of location?</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>No. The NanoDrop Home Kit is only available in select states with licensed telehealth coverage through the TheraDirect partnership.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>- No. The NanoDrop Home Kit is available only in select states with licensed telehealth coverage via TheraDirect.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Who is responsible for cloud engineering at Theranos?</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Richard Parker is the VP of Cloud Engineering at Theranos.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>- Richard Parker is the VP, Cloud Engineering at Theranos.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Leadership:  
+- Sherlock Holmes – Founder &amp; CEO  
+- Dr. Linda Templeton – Chief Science Officer  
+- Richard Parker – VP, Cloud Engineering  
+- Dr. Helen Kelly – Director of Clinical Applications  
+- Luthor Martin – General Counsel
+---
+Overview:  
+Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
+With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Which Theranos partner handles remote care distribution?</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>TelePath Global handles remote care distribution for Theranos.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1) TelePath Global (for remote care distribution)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.
+---
+Selected Partnerships:
+- Walgreens Health  
+- Cleveland Medical Research Institute  
+- United Diagnostic Alliance  
+- MedWorks Clinical Trials  
+- TelePath Global (for remote care distribution)
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>What is the reproducibility rate of Theranos test results?</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Theranos test results have a reproducibility rate between 92–97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>- Reproducibility between 92–97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>FAQs:
+Q: How accurate are Theranos test results?  
+A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
+92–97% across sample types and environments.
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+and reproducibility across a broad spectrum of biomarkers.
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>What is the exact blood sample volume the NanoDrop 3000 uses on average?</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>The NanoDrop 3000 uses an average sample volume of 1.2 microliters of capillary blood.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>- 1.2 microliters (average)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Identify Theranos’s founder-CEO and relate that role to the firm’s 2003 launch.</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Theranos was founded in 2003 by Sherlock Holmes, who also serves as CEO. In relation to the company’s 2003 launch, he has led the firm from its founding with the mission to revolutionize blood diagnostics through rapid, portable testing solutions.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1) Sherlock Holmes is Theranos’s founder and CEO.
+2) The company was founded in 2003, so Holmes founded Theranos and has served as CEO since its inception.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Overview:  
+Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
+With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
+---
+Leadership:  
+- Sherlock Holmes – Founder &amp; CEO  
+- Dr. Linda Templeton – Chief Science Officer  
+- Richard Parker – VP, Cloud Engineering  
+- Dr. Helen Kelly – Director of Clinical Applications  
+- Luthor Martin – General Counsel
 ---
 Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
@@ -589,218 +1489,44 @@
 Company Motto: “One Drop Changes Everything™”</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="120" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Which third-party health systems does TheraCloud integrate with?</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>TheraCloud integrates with EPIC, Cerner, and Apple Health via HL7 and FHIR protocols.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>TheraCloud integrates with the following third-party health systems:
-- EPIC
-- Cerner
-- Apple Health
-Integration is supported via HL7 and FHIR protocols.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Integration with third-party systems like EPIC, Cerner, and Apple Health is supported via HL7 and FHIR protocols.
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Does the NanoDrop 3000 have full FDA approval?</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>No. The NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance. It only received Emergency Use Approval for the COVID-19 MicroDrop Panel in 2021.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>- The NanoDrop 3000 does not have full FDA approval; it is CE-marked and pending full FDA 510(k) clearance for expanded panels.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0.995</v>
-      </c>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>What is MicroVial Sensing?</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MicroVial Sensing (MVS) is Theranos's next-generation detection framework combining nanophotonic arrays and adaptive sample calibration.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>- MicroVial Sensing (MVS) is a next-gen detection framework combining nanophotonic arrays and adaptive sample calibration.
-- It processes micro-samples through proprietary capillary modules, ensuring high sensitivity.
-- It is part of Theranos’s diagnostics pipeline.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Technology Platform:  
-Theranos’s diagnostics pipeline is powered by MicroVial Sensing (MVS), a next-gen detection framework combining nanophotonic arrays 
-and adaptive sample calibration. The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity
----
-Key Features:  
-- Sample volume: 1.2 microliters (average)  
-- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>When did Theranos complete its Series F and how much was raised?</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Theranos completed its Series F in Q1 2023, raising $240 million from Fidelity, BlackRock, and Sequoia Capital.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>- Series F completed in Q1 2023, raising $240M from Fidelity, BlackRock, and Sequoia Capital.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>- Completion of Series F funding round, raising $240M from Fidelity, BlackRock, and Sequoia Capital (Q1 2023)  
-- Published real-world performance results in *Clinical Diagnostics Today*, Vol. 58, Issue 4
----
-Company Name: Theranos Technologies Inc.  
-Founded: 2003  
-Founder &amp; CEO: Sherlock Holmes  
-Headquarters: Palo Alto, California  
-Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Where can I view the latest NanoDrop 3000 test menu, incl. website URL and app?</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>You can view the latest NanoDrop 3000 test menu at **theranos.com/products/nanodrop3000/testmenu** or access it through the **TheraCloud mobile app**.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>- Website: Visit theranos.com/products/nanodrop3000/testmenu
-- App: TheraCloud mobile app</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E17" s="3" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>How does Theranos’s “One Drop Changes Everything™” mission relate to NanoDrop 3000 and TheraCloud?</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Theranos’s motto, “One Drop Changes Everything™,” is reflected in both the NanoDrop 3000 and TheraCloud.
+- **NanoDrop 3000** makes the “one drop” idea practical by performing **325+ blood tests from about 1.2 microliters of blood** and delivering **lab-grade results in under 20 minutes**.
+- **TheraCloud** extends the “changes everything” part by automatically uploading results so **patients and providers can review panels, track trends over time, and get AI-powered insights**.
+Together, they support Theranos’s mission to make blood diagnostics **faster, more accessible, and more useful in real time**.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>- The motto 'One Drop Changes Everything™' captures Theranos’ belief that a single drop can unlock broad diagnostic potential, which is exemplified by NanoDrop 3000 using just 1–2 microliters of capillary blood to perform over 300 tests.
+- All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform, so patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+- Access to test menus and data is available via the TheraCloud mobile app, aligning the mission with easy, mobile-enabled data access and personalized insights.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
@@ -809,47 +1535,59 @@
 investorrelations@theranos.com
 Company Motto: “One Drop Changes Everything™”
 ---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
 Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>How do NanoDrop 3000 specs link 325+ assays with just 1–2 µL capillary blood?</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>The NanoDrop 3000 links its 325+ assays to just 1–2 µL of capillary blood through Theranos’s proprietary diagnostics platform. According to the context, it uses an average sample volume of 1.2 microliters and combines microfluidics, spectrometry, and the patented NanoAnalysis Engine™ to deliver lab-grade results. Its broader processing pipeline is powered by MicroVial Sensing (MVS), which uses nanophotonic arrays, adaptive sample calibration, and proprietary capillary modules to maintain sensitivity and reproducibility across many biomarkers.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>- The NanoDrop 3000 links 325+ assays to a tiny input by using microfluidics, spectrometry, and Theranos’s NanoAnalysis Engine to process many tests from a single small sample.
-- Its average sample volume is 1.2 microliters, which is possible because the integrated microfluidics handle and direct the tiny capillary blood volume into multiple assays detected by spectrometry.
-- The test menu comprises 325+ assays across metabolic, hormonal, infectious, hematologic, and genomic panels, all derived from that small sample through the NanoAnalysis Engine’s analysis.
-- Results are delivered on-device and can be synced via the Theracloud platform, enabling rapid access to the broad assay results from a single 1–2 µL capillary blood input.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>How do NanoDrop 3000’s 1–2 µL samples enable 325+ assays with lab-grade results?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>NanoDrop 3000 achieves 325+ assays from just 1–2 µL of blood by combining microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™. Its MicroVial Sensing (MVS) platform uses nanophotonic arrays, adaptive sample calibration, and proprietary capillary modules to process micro-samples with high sensitivity and reproducibility across many biomarkers. According to the company, this enables lab-grade results in under 20 minutes, with independent studies reporting over 94% sensitivity and specificity for most core assays.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>- The NanoDrop 3000 uses microfluidics to precisely handle very small sample volumes (about 1–2 µL, with an average of 1.2 µL) so that multiple assays can be run from a tiny capillary blood sample. 
+- It combines spectrometry with Theranos’s NanoAnalysis Engine to analyze the tiny sample and generate assay results, enabling access to 325+ tests. 
+- The large assay menu spans metabolic, hormonal, infectious, hematologic, and genomic panels, all delivered via an on-device display and synchronized to the TheraCloud platform for lab-grade results. 
+- The system’s lab-grade reliability is supported by certifications: Theranos labs are CLIA-certified and CAP-accredited, and the NanoDrop 3000 is CE-marked (with full FDA 510(k) clearance for expanded panels pending).</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
@@ -858,87 +1596,57 @@
 Key Features:  
 - Sample volume: 1.2 microliters (average)  
 - Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0.996</v>
-      </c>
-    </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Who leads Theranos Technologies Inc., the 2003-founded Palo Alto blood-diagnostics firm behind NanoDrop 3000?</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Theranos Technologies Inc. is led by Sherlock Holmes, the Founder &amp; CEO. The company was founded in 2003 and is headquartered in Palo Alto, California.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1) Sherlock Holmes leads Theranos Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Company Name: Theranos Technologies Inc.  
-Founded: 2003  
-Founder &amp; CEO: Sherlock Holmes  
-Headquarters: Palo Alto, California  
-Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
----
-Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Which secure web/mobile portal auto-syncs NanoDrop 3000 results for pt/provider review?</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>TheraCloud™. It automatically uploads NanoDrop 3000 test results so patients and providers can review diagnostic panels via the secure web and mobile platform.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>- TheraCloud™ Health Portal (TheraCloud) auto-syncs NanoDrop 3000 results for patient and provider review.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.856</v>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>How do on-device output and TheraCloud syncing jointly deliver NanoDrop 3000 results?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>NanoDrop 3000 delivers results in two ways: they appear directly on the device’s display for immediate review, and they are also synced to TheraCloud™ for secure access via web or mobile. Through TheraCloud, patients and providers can view full panels, track trends over time, and integrate data with systems like EPIC, Cerner, and Apple Health.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1) On-device output: results are shown on the NanoDrop 3000's on-device display.\n2) TheraCloud syncing: results are automatically uploaded to TheraCloud, enabling web/mobile access and secure storage.\n3) Joint delivery: users can view full diagnostic panels, trend health data over time, and receive AI-powered insights via TheraCloud, while the device also presents immediate local results.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>TheraCloud™ Health Portal:  
 All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
@@ -946,42 +1654,59 @@
 ---
 Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>What motto does Palo Alto-based Theranos, maker of NanoDrop 3000 synced via TheraCloud, use?</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Theranos’s motto is: “One Drop Changes Everything™”</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>- Motto: “One Drop Changes Everything™”</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.894</v>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Where is the NanoDrop 3000 325+ assay test menu available online or in-app?</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>The NanoDrop 3000 test menu is available at **theranos.com/products/nanodrop3000/testmenu** or through the **TheraCloud mobile app**.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>- Online: Visit theranos.com/products/nanodrop3000/testmenu.
+- In-app: Access via the TheraCloud mobile app.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
@@ -990,25 +1715,343 @@
 investorrelations@theranos.com
 Company Motto: “One Drop Changes Everything™”
 ---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
 TheraCloud™ Health Portal:  
 All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>1</v>
+      <c r="F21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Where can I view NanoDrop 3000's latest test menu, incl. via TheraCloud app?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>You can view the latest NanoDrop 3000 test menu at **theranos.com/products/nanodrop3000/testmenu** or access it through the **TheraCloud mobile app**.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>- Visit theranos.com/products/nanodrop3000/testmenu to view the latest test menu.\n- Or access the test menu via the Theranos TheraCloud mobile app.\n- In the Theracos Cloud Health Portal, all NanoDrop 3000 tests are automatically uploaded so you can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.\n- The test menu includes 325+ assays across metabolic, hormonal, infectious, hematologic, and genomic panels.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Where can I access NanoDrop 3000’s latest test menu: theranos.com link or TheraCloud app?</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>You can access the latest NanoDrop 3000 test menu at **theranos.com/products/nanodrop3000/testmenu** or through the **TheraCloud mobile app**.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>- Visit theranos.com/products/nanodrop3000/testmenu
+- Access via the TheraCloud mobile app</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Identify Theranos founder-CEO and relate this role to the firm’s 2003 launch.</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Sherlock Holmes is the Founder &amp; CEO of Theranos Technologies Inc. Since the company was founded in 2003, this means he both launched the firm and continues to lead it as chief executive.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1. The founder-CEO is Sherlock Holmes.
+2. He founded Theranos Technologies Inc. in 2003, tying the founder-CEO role to the firm’s launch year.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Overview:  
+Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
+With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
+---
+Leadership:  
+- Sherlock Holmes – Founder &amp; CEO  
+- Dr. Linda Templeton – Chief Science Officer  
+- Richard Parker – VP, Cloud Engineering  
+- Dr. Helen Kelly – Director of Clinical Applications  
+- Luthor Martin – General Counsel
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Compare Theranos’s mission and company motto.</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Theranos’s mission is to revolutionize blood diagnostics through rapid, portable testing solutions, while its motto, “One Drop Changes Everything™,” expresses that goal in a short, memorable way by emphasizing the impact of small-volume blood testing.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>- Mission describes Theranos’ primary objective: to revolutionize blood diagnostics through rapid, portable testing solutions.
+- The company motto is a branding phrase that emphasizes the impact of a single blood drop, stated as “One Drop Changes Everything™”.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Overview:  
+Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
+With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”
+---
+Technology Platform:  
+Theranos’s diagnostics pipeline is powered by MicroVial Sensing (MVS), a next-gen detection framework combining nanophotonic arrays 
+and adaptive sample calibration. The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>If avg sample is 1–2 µL capillary blood, how many assays can NanoDrop 3000 run?</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>NanoDrop 3000 can run over 300 blood tests; the test menu includes 325+ assays using about 1–2 microliters of capillary blood.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>- Approximately 325+ assays (over 300) can be run using an average sample of 1–2 µL capillary blood.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+FAQs:
+Q: How accurate are Theranos test results?  
+A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
+92–97% across sample types and environments.
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -1054,7 +2097,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.583</v>
+        <v>0.221</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
@@ -1069,7 +2112,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
@@ -1084,7 +2127,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.95</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
@@ -1099,7 +2142,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.999</v>
+        <v>0.982</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -1114,7 +2157,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.999</v>
+        <v>0.981</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>

--- a/RAGEvaluation_report.xlsx
+++ b/RAGEvaluation_report.xlsx
@@ -205,6 +205,66 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>RAG Evaluator</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>The question asked to the RAG agent.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>The ideal/golden answer for the query.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>The answer generated by the RAG agent.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Source snippets cited by the RAG agent in its answer.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>The chunks retrieved from ChromaDB for the query.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Measures if retrieved chunks are relevant to the query. Failing = chunks contain noise.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Measures if retrieved chunks contain all info needed to answer the query.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Measures if the most relevant chunks are ranked first in retrieval.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Measures if the generated answer is correct and complete given the query.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Measures if citations in the answer are accurate and supported by retrieved context.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,18 +556,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -528,30 +589,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Citations</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Retrieved Context</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Contextual_Relevancy</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Contextual_Recall</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Contextual_Precision</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Answer_Correctness</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Citation_Accuracy</t>
         </is>
@@ -570,10 +636,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>- The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood.\n- It integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to enable rapid testing.\n- Key features include a sample volume of about 1.2 microliters (average) and a test menu of 325+ assays, with results delivered on-device and synced via the TheraCloud platform.</t>
+          <t>{
+  "answer": "- The NanoDrop 3000 is Theranos’ flagship product.\n- It is a compact, portable diagnostic device.\n- It can perform over 300 blood tests using just 1–2 microliters of capillary blood.\n- It integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™.",
+  "citations": [
+    "Flagship Product: NanoDrop 3000™",
+    "The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™."
+  ]
+}</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>• Flagship Product: NanoDrop 3000™
+• The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
@@ -588,31 +666,22 @@
 ---
 Q: What certifications does Theranos hold?  
 A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
----
-Key Features:  
-- Sample volume: 1.2 microliters (average)  
-- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
+panels.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0.7</v>
-      </c>
       <c r="H2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -629,12 +698,20 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>- EPIC
-- Cerner
-- Apple Health</t>
+          <t>{
+  "answer": "- EPIC\n- Cerner\n- Apple Health (via HL7 and FHIR protocols)",
+  "citations": [
+    "Integration with third-party systems like EPIC, Cerner, and Apple Health is supported via HL7 and FHIR protocols."
+  ]
+}</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>• Integration with third-party systems like EPIC, Cerner, and Apple Health is supported via HL7 and FHIR protocols.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Integration with third-party systems like EPIC, Cerner, and Apple Health is supported via HL7 and FHIR protocols.
 ---
@@ -647,141 +724,131 @@
 - Cleveland Medical Research Institute  
 - United Diagnostic Alliance  
 - MedWorks Clinical Trials  
-- TelePath Global (for remote care distribution)
+- TelePath Global (for remote care distribution)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Does the NanoDrop 3000 have full FDA approval?</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No. The NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance. It only received Emergency Use Approval for the COVID-19 MicroDrop Panel in 2021.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "1. No. The NanoDrop 3000 does not have full FDA approval yet; it is CE-marked and pending full FDA 510(k) clearance for expanded panels.\n2. It has FDA Emergency Use Approval for the COVID-19 MicroDrop Panel (2021).",
+  "citations": [
+    "\"NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded panels.\"",
+    "\"FDA Emergency Use Approval granted for the COVID-19 MicroDrop Panel (2021).\""
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>• "NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded panels."
+• "FDA Emergency Use Approval granted for the COVID-19 MicroDrop Panel (2021)."</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.
+---
+Recent Milestones:
+- FDA Emergency Use Approval granted for the COVID-19 MicroDrop Panel (2021)  
+- Expanded test menu to include pharmacogenomic testing (Q3 2022)  
+- Strategic licensing deal signed with Medix Korea for Asia-Pacific rollout</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>What is MicroVial Sensing?</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>MicroVial Sensing (MVS) is Theranos's next-generation detection framework combining nanophotonic arrays and adaptive sample calibration.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- MicroVial Sensing (MVS) is Theranos’s next-gen detection framework that combines nanophotonic arrays and adaptive sample calibration.\n- It processes micro-samples through proprietary capillary modules to ensure high sensitivity.",
+  "citations": [
+    "MicroVial Sensing (MVS) is Theranos’s diagnostics pipeline powered by a next-gen detection framework combining nanophotonic arrays and adaptive sample calibration.",
+    "The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>• MicroVial Sensing (MVS) is Theranos’s diagnostics pipeline powered by a next-gen detection framework combining nanophotonic arrays and adaptive sample calibration.
+• The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Technology Platform:  
+Theranos’s diagnostics pipeline is powered by MicroVial Sensing (MVS), a next-gen detection framework combining nanophotonic arrays 
+and adaptive sample calibration. The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity
 ---
 Key Features:  
 - Sample volume: 1.2 microliters (average)  
 - Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
 - Results delivery: On-device display and synced via TheraCloud™ platform
 ---
-reduces cost, increases accessibility, and accelerates clinical decision-making, putting real-time health information in the 
-hands of patients and physicians alike.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="120" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Does the NanoDrop 3000 have full FDA approval?</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>No. The NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance. It only received Emergency Use Approval for the COVID-19 MicroDrop Panel in 2021.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>- No. The NanoDrop 3000 is CE-marked but FDA 510(k) clearance for expanded panels is still pending.
-- It does have FDA Emergency Use Approval for the COVID-19 MicroDrop Panel (2021).
-- Therefore, full FDA approval has not been granted yet.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
----
-Recent Milestones:
-- FDA Emergency Use Approval granted for the COVID-19 MicroDrop Panel (2021)  
-- Expanded test menu to include pharmacogenomic testing (Q3 2022)  
-- Strategic licensing deal signed with Medix Korea for Asia-Pacific rollout
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>What is MicroVial Sensing?</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MicroVial Sensing (MVS) is Theranos's next-generation detection framework combining nanophotonic arrays and adaptive sample calibration.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>- MicroVial Sensing (MVS) is a next-gen detection framework that combines nanophotonic arrays and adaptive sample calibration.
-- The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Technology Platform:  
-Theranos’s diagnostics pipeline is powered by MicroVial Sensing (MVS), a next-gen detection framework combining nanophotonic arrays 
-and adaptive sample calibration. The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity
----
-Key Features:  
-- Sample volume: 1.2 microliters (average)  
-- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform
----
 Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Recent Milestones:
-- FDA Emergency Use Approval granted for the COVID-19 MicroDrop Panel (2021)  
-- Expanded test menu to include pharmacogenomic testing (Q3 2022)  
-- Strategic licensing deal signed with Medix Korea for Asia-Pacific rollout
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.625</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>1</v>
@@ -790,6 +857,9 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -806,11 +876,20 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>- Completed Series F in Q1 2023.
-- Raised $240 million from Fidelity, BlackRock, and Sequoia Capital.</t>
+          <t>{
+  "answer": "- Completed Series F in Q1 2023\n- Raised $240M from Fidelity, BlackRock, and Sequoia Capital",
+  "citations": [
+    "Completion of Series F funding round, raising $240M from Fidelity, BlackRock, and Sequoia Capital (Q1 2023)"
+  ]
+}</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>• Completion of Series F funding round, raising $240M from Fidelity, BlackRock, and Sequoia Capital (Q1 2023)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>- Completion of Series F funding round, raising $240M from Fidelity, BlackRock, and Sequoia Capital (Q1 2023)  
 - Published real-world performance results in *Clinical Diagnostics Today*, Vol. 58, Issue 4
@@ -824,23 +903,11 @@
 Corporate Structure:  
 Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
 The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Overview:  
-Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
-With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
----
-FAQs:
-Q: How accurate are Theranos test results?  
-A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
-92–97% across sample types and environments.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
+in the U.S.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.125</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>1</v>
@@ -849,6 +916,9 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -865,10 +935,20 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>- Not universally available. The NanoDrop Home Kit is available in select states with licensed telehealth coverage, through the TheraDirect partnership; patients in those states can request it.</t>
+          <t>{
+  "answer": "- The NanoDrop Home Kit is available through TheraDirect and can be requested, but it is only available in select states with licensed telehealth coverage.\n- It is not available in every location; eligibility depends on state and licensed telehealth coverage.",
+  "citations": [
+    "Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed telehealth coverage."
+  ]
+}</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>• Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Q: Can Theranos tests be administered at home?  
 A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
@@ -877,609 +957,6 @@
 Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
 of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0.982</v>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Who is responsible for cloud engineering at Theranos?</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Richard Parker is the VP of Cloud Engineering at Theranos.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>- Richard Parker – VP, Cloud Engineering</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Corporate Structure:  
-Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
-The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Company Name: Theranos Technologies Inc.  
-Founded: 2003  
-Founder &amp; CEO: Sherlock Holmes  
-Headquarters: Palo Alto, California  
-Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
----
-Leadership:  
-- Sherlock Holmes – Founder &amp; CEO  
-- Dr. Linda Templeton – Chief Science Officer  
-- Richard Parker – VP, Cloud Engineering  
-- Dr. Helen Kelly – Director of Clinical Applications  
-- Luthor Martin – General Counsel
----
-Overview:  
-Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
-With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Which Theranos partner handles remote care distribution?</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>TelePath Global handles remote care distribution for Theranos.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>- TelePath Global (for remote care distribution).</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Corporate Structure:  
-Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
-The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.
----
-Selected Partnerships:
-- Walgreens Health  
-- Cleveland Medical Research Institute  
-- United Diagnostic Alliance  
-- MedWorks Clinical Trials  
-- TelePath Global (for remote care distribution)
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
----
-Company Name: Theranos Technologies Inc.  
-Founded: 2003  
-Founder &amp; CEO: Sherlock Holmes  
-Headquarters: Palo Alto, California  
-Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>What is the reproducibility rate of Theranos test results?</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Theranos test results have a reproducibility rate between 92â€“97% across sample types and environments.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>- Reproducibility between 92–97% across sample types and environments.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>FAQs:
-Q: How accurate are Theranos test results?  
-A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
-92–97% across sample types and environments.
----
-Corporate Structure:  
-Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
-The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
----
-and reproducibility across a broad spectrum of biomarkers.
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>What is the exact blood sample volume the NanoDrop 3000 uses on average?</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>The NanoDrop 3000 uses an average sample volume of 1.2 microliters of capillary blood.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>- 1.2 microliters (average)</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Key Features:  
-- Sample volume: 1.2 microliters (average)  
-- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Can anyone use the NanoDrop Home Kit regardless of location?</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>No. The NanoDrop Home Kit is only available in select states with licensed telehealth coverage through the TheraDirect partnership.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>- No. The NanoDrop Home Kit is available only in select states with licensed telehealth coverage via TheraDirect.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.
----
-Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0.995</v>
-      </c>
-    </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Who is responsible for cloud engineering at Theranos?</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Richard Parker is the VP of Cloud Engineering at Theranos.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>- Richard Parker is the VP, Cloud Engineering at Theranos.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Corporate Structure:  
-Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
-The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Company Name: Theranos Technologies Inc.  
-Founded: 2003  
-Founder &amp; CEO: Sherlock Holmes  
-Headquarters: Palo Alto, California  
-Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
----
-Leadership:  
-- Sherlock Holmes – Founder &amp; CEO  
-- Dr. Linda Templeton – Chief Science Officer  
-- Richard Parker – VP, Cloud Engineering  
-- Dr. Helen Kelly – Director of Clinical Applications  
-- Luthor Martin – General Counsel
----
-Overview:  
-Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
-With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Which Theranos partner handles remote care distribution?</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>TelePath Global handles remote care distribution for Theranos.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1) TelePath Global (for remote care distribution)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Corporate Structure:  
-Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
-The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.
----
-Selected Partnerships:
-- Walgreens Health  
-- Cleveland Medical Research Institute  
-- United Diagnostic Alliance  
-- MedWorks Clinical Trials  
-- TelePath Global (for remote care distribution)
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
----
-Company Name: Theranos Technologies Inc.  
-Founded: 2003  
-Founder &amp; CEO: Sherlock Holmes  
-Headquarters: Palo Alto, California  
-Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>What is the reproducibility rate of Theranos test results?</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Theranos test results have a reproducibility rate between 92–97% across sample types and environments.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>- Reproducibility between 92–97% across sample types and environments.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>FAQs:
-Q: How accurate are Theranos test results?  
-A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
-92–97% across sample types and environments.
----
-Corporate Structure:  
-Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
-The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
----
-and reproducibility across a broad spectrum of biomarkers.
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>What is the exact blood sample volume the NanoDrop 3000 uses on average?</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>The NanoDrop 3000 uses an average sample volume of 1.2 microliters of capillary blood.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>- 1.2 microliters (average)</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Key Features:  
-- Sample volume: 1.2 microliters (average)  
-- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Identify Theranos’s founder-CEO and relate that role to the firm’s 2003 launch.</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Theranos was founded in 2003 by Sherlock Holmes, who also serves as CEO. In relation to the company’s 2003 launch, he has led the firm from its founding with the mission to revolutionize blood diagnostics through rapid, portable testing solutions.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>1) Sherlock Holmes is Theranos’s founder and CEO.
-2) The company was founded in 2003, so Holmes founded Theranos and has served as CEO since its inception.</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Company Name: Theranos Technologies Inc.  
-Founded: 2003  
-Founder &amp; CEO: Sherlock Holmes  
-Headquarters: Palo Alto, California  
-Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
----
-Corporate Structure:  
-Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
-The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Overview:  
-Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
-With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
----
-Leadership:  
-- Sherlock Holmes – Founder &amp; CEO  
-- Dr. Linda Templeton – Chief Science Officer  
-- Richard Parker – VP, Cloud Engineering  
-- Dr. Helen Kelly – Director of Clinical Applications  
-- Luthor Martin – General Counsel
 ---
 Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
@@ -1489,20 +966,632 @@
 Company Motto: “One Drop Changes Everything™”</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>1</v>
+      <c r="F7" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Who is responsible for cloud engineering at Theranos?</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Richard Parker is the VP of Cloud Engineering at Theranos.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- Richard Parker – VP, Cloud Engineering.",
+  "citations": [
+    "Richard Parker – VP, Cloud Engineering"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>• Richard Parker – VP, Cloud Engineering</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Leadership:  
+- Sherlock Holmes – Founder &amp; CEO  
+- Dr. Linda Templeton – Chief Science Officer  
+- Richard Parker – VP, Cloud Engineering  
+- Dr. Helen Kelly – Director of Clinical Applications  
+- Luthor Martin – General Counsel</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Which Theranos partner handles remote care distribution?</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>TelePath Global handles remote care distribution for Theranos.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- TelePath Global handles remote care distribution.",
+  "citations": [
+    "TelePath Global (for remote care distribution)"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>• TelePath Global (for remote care distribution)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.
+---
+Selected Partnerships:
+- Walgreens Health  
+- Cleveland Medical Research Institute  
+- United Diagnostic Alliance  
+- MedWorks Clinical Trials  
+- TelePath Global (for remote care distribution)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>What is the reproducibility rate of Theranos test results?</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Theranos test results have a reproducibility rate between 92â€“97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- Reproducibility rate: 92–97% across sample types and environments.",
+  "citations": [
+    "reproducibility between 92–97% across sample types and environments."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>• reproducibility between 92–97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>FAQs:
+Q: How accurate are Theranos test results?  
+A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
+92–97% across sample types and environments.
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>What is the exact blood sample volume the NanoDrop 3000 uses on average?</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>The NanoDrop 3000 uses an average sample volume of 1.2 microliters of capillary blood.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- The NanoDrop 3000 uses 1.2 microliters (average) of blood.",
+  "citations": [
+    "Sample volume: 1.2 microliters (average)"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>• Sample volume: 1.2 microliters (average)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Can anyone use the NanoDrop Home Kit regardless of location?</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>No. The NanoDrop Home Kit is only available in select states with licensed telehealth coverage through the TheraDirect partnership.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- No. The NanoDrop Home Kit is available only in select states with licensed telehealth coverage through the TheraDirect partnership.",
+  "citations": [
+    "Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed telehealth coverage."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>• Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.973</v>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Who is responsible for cloud engineering at Theranos?</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Richard Parker is the VP of Cloud Engineering at Theranos.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "1) Richard Parker – VP, Cloud Engineering",
+  "citations": [
+    "Richard Parker – VP, Cloud Engineering"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>• Richard Parker – VP, Cloud Engineering</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Leadership:  
+- Sherlock Holmes – Founder &amp; CEO  
+- Dr. Linda Templeton – Chief Science Officer  
+- Richard Parker – VP, Cloud Engineering  
+- Dr. Helen Kelly – Director of Clinical Applications  
+- Luthor Martin – General Counsel</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Which Theranos partner handles remote care distribution?</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>TelePath Global handles remote care distribution for Theranos.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- TelePath Global handles remote care distribution.",
+  "citations": [
+    "TelePath Global (for remote care distribution)",
+    "Selected Partnerships: TelePath Global (for remote care distribution)"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>• TelePath Global (for remote care distribution)
+• Selected Partnerships: TelePath Global (for remote care distribution)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: Can Theranos tests be administered at home?  
+A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
+telehealth coverage.
+---
+Selected Partnerships:
+- Walgreens Health  
+- Cleveland Medical Research Institute  
+- United Diagnostic Alliance  
+- MedWorks Clinical Trials  
+- TelePath Global (for remote care distribution)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>What is the reproducibility rate of Theranos test results?</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Theranos test results have a reproducibility rate between 92–97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- Reproducibility: 92–97% across sample types and environments.",
+  "citations": [
+    "Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 92–97% across sample types and environments."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>• Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 92–97% across sample types and environments.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>FAQs:
+Q: How accurate are Theranos test results?  
+A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
+92–97% across sample types and environments.
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Q: What certifications does Theranos hold?  
+A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
+panels.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>What is the exact blood sample volume the NanoDrop 3000 uses on average?</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>The NanoDrop 3000 uses an average sample volume of 1.2 microliters of capillary blood.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "- 1.2 microliters (average)",
+  "citations": [
+    "Sample volume: 1.2 microliters (average)"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>• Sample volume: 1.2 microliters (average)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
+---
+Key Features:  
+- Sample volume: 1.2 microliters (average)  
+- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
+- Results delivery: On-device display and synced via TheraCloud™ platform
+---
+Q: Where can I view the latest test menu?  
+A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+Media Contacts:  
+press@theranos.com  
+investorrelations@theranos.com
+Company Motto: “One Drop Changes Everything™”</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Identify Theranos’s founder-CEO and relate that role to the firm’s 2003 launch.</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Theranos was founded in 2003 by Sherlock Holmes, who also serves as CEO. In relation to the company’s 2003 launch, he has led the firm from its founding with the mission to revolutionize blood diagnostics through rapid, portable testing solutions.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "1) Sherlock Holmes is Theranos Technologies Inc.'s founder and CEO.\n2) The company was founded in 2003, so Holmes's role as founder-CEO aligns with the 2003 launch.",
+  "citations": [
+    "Founder &amp; CEO: Sherlock Holmes",
+    "Founded: 2003"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>• Founder &amp; CEO: Sherlock Holmes
+• Founded: 2003</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Company Name: Theranos Technologies Inc.  
+Founded: 2003  
+Founder &amp; CEO: Sherlock Holmes  
+Headquarters: Palo Alto, California  
+Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.
+---
+Corporate Structure:  
+Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
+The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
+in the U.S.
+---
+Overview:  
+Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
+With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.222</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.806</v>
+        <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.992</v>
+        <v>0.964</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.982</v>
       </c>
     </row>
     <row r="18" ht="120" customHeight="1">
@@ -1521,12 +1610,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>- The motto 'One Drop Changes Everything™' captures Theranos’ belief that a single drop can unlock broad diagnostic potential, which is exemplified by NanoDrop 3000 using just 1–2 microliters of capillary blood to perform over 300 tests.
-- All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform, so patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
-- Access to test menus and data is available via the TheraCloud mobile app, aligning the mission with easy, mobile-enabled data access and personalized insights.</t>
+          <t>{
+  "answer": "1. The mission \"One Drop Changes Everything™\" emphasizes enabling diagnostics from a single drop, which NanoDrop 3000 demonstrates by performing over 300 tests from just 1–2 microliters of capillary blood.\n2. TheraCloud supports this by automatically uploading all NanoDrop 3000 tests to its secure platform, where patients and providers can review full diagnostic panels, track health data over time, and receive AI-powered personalized insights.\n3. Together, the motto, NanoDrop 3000's high-test-per-drop capability, and TheraCloud's cloud-based data review and insights illustrate how a single drop can drive broad testing and ongoing, data-driven care.",
+  "citations": [
+    "\"One Drop Changes Everything™\"",
+    "The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood.",
+    "All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics."
+  ]
+}</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>• "One Drop Changes Everything™"
+• The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood.
+• All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
@@ -1541,31 +1642,23 @@
 ---
 Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F18" s="3" t="n">
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H18" s="4" t="n">
-        <v>0.9379999999999999</v>
+        <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.95</v>
+        <v>0.997</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.962</v>
       </c>
     </row>
     <row r="19" ht="120" customHeight="1">
@@ -1581,13 +1674,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>- The NanoDrop 3000 uses microfluidics to precisely handle very small sample volumes (about 1–2 µL, with an average of 1.2 µL) so that multiple assays can be run from a tiny capillary blood sample. 
-- It combines spectrometry with Theranos’s NanoAnalysis Engine to analyze the tiny sample and generate assay results, enabling access to 325+ tests. 
-- The large assay menu spans metabolic, hormonal, infectious, hematologic, and genomic panels, all delivered via an on-device display and synchronized to the TheraCloud platform for lab-grade results. 
-- The system’s lab-grade reliability is supported by certifications: Theranos labs are CLIA-certified and CAP-accredited, and the NanoDrop 3000 is CE-marked (with full FDA 510(k) clearance for expanded panels pending).</t>
+          <t>{
+  "answer": "- The NanoDrop 3000 uses an average sample volume of 1.2 µL to run a test menu of 325+ assays.\n- This capability is enabled by the device’s integration of microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ which process and analyze measurements from such small samples.\n- The broad test coverage includes metabolic, hormonal, infectious, hematologic, and genomic panels.\n- Results are delivered on-device and can be synced via the TherCloud platform for convenient access and record-keeping.",
+  "citations": [
+    "The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood.",
+    "Key Features: - Sample volume: 1.2 microliters (average) - Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels - Results delivery: On-device display and synced via TheraCloud™ platform",
+    "The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide"
+  ]
+}</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>• The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood.
+• Key Features: - Sample volume: 1.2 microliters (average) - Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels - Results delivery: On-device display and synced via TheraCloud™ platform
+• The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
@@ -1600,93 +1704,87 @@
 ---
 Q: What certifications does Theranos hold?  
 A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
+panels.</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0.896</v>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>How do on-device output and TheraCloud syncing jointly deliver NanoDrop 3000 results?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>NanoDrop 3000 delivers results in two ways: they appear directly on the device’s display for immediate review, and they are also synced to TheraCloud™ for secure access via web or mobile. Through TheraCloud, patients and providers can view full panels, track trends over time, and integrate data with systems like EPIC, Cerner, and Apple Health.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "answer": "1) The NanoDrop 3000 generates test results on-device using its microfluidics, spectrometry, and the NanoAnalysis Engine.\n2) All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform.\n3) On TheraCloud, patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.\n4) Results can be accessed via the TheraCloud mobile app, and you can view the latest test menu at theranos.com/products/nanodrop3000/testmenu.",
+  "citations": [
+    "\"All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.\"",
+    "\"The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™\"",
+    "\"Where can I view the latest test menu? A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.\""
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>• "All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics."
+• "The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™"
+• "Where can I view the latest test menu? A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app."</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>TheraCloud™ Health Portal:  
+All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
+can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+---
+Flagship Product: NanoDrop 3000™  
+The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
+of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
 ---
 Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
 Media Contacts:  
 press@theranos.com  
 investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" s="3" t="n">
+Company Motto: “One Drop Changes Everything™”</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>0.333</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0.856</v>
-      </c>
-    </row>
-    <row r="20" ht="120" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>How do on-device output and TheraCloud syncing jointly deliver NanoDrop 3000 results?</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>NanoDrop 3000 delivers results in two ways: they appear directly on the device’s display for immediate review, and they are also synced to TheraCloud™ for secure access via web or mobile. Through TheraCloud, patients and providers can view full panels, track trends over time, and integrate data with systems like EPIC, Cerner, and Apple Health.</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>1) On-device output: results are shown on the NanoDrop 3000's on-device display.\n2) TheraCloud syncing: results are automatically uploaded to TheraCloud, enabling web/mobile access and secure storage.\n3) Joint delivery: users can view full diagnostic panels, trend health data over time, and receive AI-powered insights via TheraCloud, while the device also presents immediate local results.</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
----
-Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”
----
-Key Features:  
-- Sample volume: 1.2 microliters (average)  
-- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0.75</v>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.9320000000000001</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.894</v>
+        <v>0.844</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.841</v>
       </c>
     </row>
     <row r="21" ht="120" customHeight="1">
@@ -1702,11 +1800,20 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>- Online: Visit theranos.com/products/nanodrop3000/testmenu.
-- In-app: Access via the TheraCloud mobile app.</t>
+          <t>{
+  "answer": "- Online: Visit theranos.com/products/nanodrop3000/testmenu\n- In-app: Access via the TheraCloud mobile app",
+  "citations": [
+    "Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app."
+  ]
+}</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>• Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
@@ -1722,30 +1829,22 @@
 Key Features:  
 - Sample volume: 1.2 microliters (average)  
 - Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform
----
-TheraCloud™ Health Portal:  
-All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform. Patients and providers 
-can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>1</v>
+- Results delivery: On-device display and synced via TheraCloud™ platform</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.286</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="I21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1762,10 +1861,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>- Visit theranos.com/products/nanodrop3000/testmenu to view the latest test menu.\n- Or access the test menu via the Theranos TheraCloud mobile app.\n- In the Theracos Cloud Health Portal, all NanoDrop 3000 tests are automatically uploaded so you can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.\n- The test menu includes 325+ assays across metabolic, hormonal, infectious, hematologic, and genomic panels.</t>
+          <t>{
+  "answer": "- Web: Visit theranos.com/products/nanodrop3000/testmenu to view the latest NanoDrop 3000 test menu.\n- TheraCloud mobile app: Access the latest test menu via the TheraCloud mobile app.\n- TheraCloud Health Portal: All NanoDrop 3000 tests are automatically uploaded to TheraCloud, and you can review full diagnostic panels, trend health data over time, and receive personalized AI-powered insights.\n- Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels.",
+  "citations": [
+    "Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.",
+    "All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform.",
+    "Patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.",
+    "Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels."
+  ]
+}</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>• Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
+• All NanoDrop 3000 tests are automatically uploaded to TheraCloud, Theranos’s secure web and mobile platform.
+• Patients and providers can review full diagnostic panels, trend health data over time, and receive personalized insights based on AI-powered analytics.
+• Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
@@ -1781,31 +1896,23 @@
 Key Features:  
 - Sample volume: 1.2 microliters (average)  
 - Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels  
-- Results delivery: On-device display and synced via TheraCloud™ platform
----
-Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Q: Can Theranos tests be administered at home?  
-A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>1</v>
+- Results delivery: On-device display and synced via TheraCloud™ platform</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.927</v>
+        <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.996</v>
+        <v>0.956</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="120" customHeight="1">
@@ -1821,11 +1928,20 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>- Visit theranos.com/products/nanodrop3000/testmenu
-- Access via the TheraCloud mobile app</t>
+          <t>{
+  "answer": "1. Visit theranos.com/products/nanodrop3000/testmenu\n2. Access via the TheraCloud mobile app",
+  "citations": [
+    "\"Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.\""
+  ]
+}</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>• "Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app."</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Q: Where can I view the latest test menu?  
 A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
@@ -1840,23 +1956,12 @@
 ---
 Q: Can Theranos tests be administered at home?  
 A: Yes. Through our partnership with TheraDirect™, patients can request a NanoDrop Home Kit, available in select states with licensed 
-telehealth coverage.
----
-Flagship Product: NanoDrop 3000™  
-The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
-of capillary blood. The device integrates microfluidics, spectrometry, and Theranos’s patented NanoAnalysis Engine™ to provide
----
-Q: What certifications does Theranos hold?  
-A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
+telehealth coverage.</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G23" s="4" t="n">
         <v>1</v>
       </c>
@@ -1864,7 +1969,10 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.998</v>
+        <v>1</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="120" customHeight="1">
@@ -1880,11 +1988,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1. The founder-CEO is Sherlock Holmes.
-2. He founded Theranos Technologies Inc. in 2003, tying the founder-CEO role to the firm’s launch year.</t>
+          <t>{
+  "answer": "- Sherlock Holmes is Theranos Technologies Inc.'s founder and CEO.\n- The company was founded in 2003.",
+  "citations": [
+    "\"Founder &amp; CEO: Sherlock Holmes\"",
+    "\"Founded: 2003\""
+  ]
+}</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>• "Founder &amp; CEO: Sherlock Holmes"
+• "Founded: 2003"</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Company Name: Theranos Technologies Inc.  
 Founded: 2003  
@@ -1899,36 +2018,22 @@
 ---
 Overview:  
 Theranos Technologies Inc. is a medical technology company dedicated to transforming how blood diagnostics are performed. 
-With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation
----
-Leadership:  
-- Sherlock Holmes – Founder &amp; CEO  
-- Dr. Linda Templeton – Chief Science Officer  
-- Richard Parker – VP, Cloud Engineering  
-- Dr. Helen Kelly – Director of Clinical Applications  
-- Luthor Martin – General Counsel
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>1</v>
+With its proprietary platform, Theranos enables comprehensive laboratory testing from a few drops of blood. This innovation</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.333</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.978</v>
+        <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="J24" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1945,11 +2050,20 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>- Mission describes Theranos’ primary objective: to revolutionize blood diagnostics through rapid, portable testing solutions.
-- The company motto is a branding phrase that emphasizes the impact of a single blood drop, stated as “One Drop Changes Everything™”.</t>
+          <t>{
+  "answer": "- Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.\n- Motto in the provided context: not specified.\n- Conclusion: A direct comparison isn't possible with the given information; please provide Theranos' motto to enable a comparison.",
+  "citations": [
+    "Mission: To revolutionize blood diagnostics through rapid, portable testing solutions."
+  ]
+}</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>• Mission: To revolutionize blood diagnostics through rapid, portable testing solutions.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Company Name: Theranos Technologies Inc.  
 Founded: 2003  
@@ -1964,34 +2078,23 @@
 Corporate Structure:  
 Theranos employs over 1,800 staff across R&amp;D, diagnostics engineering, cloud systems, regulatory science, and clinical operations. 
 The company maintains clinical partnerships with over 60 healthcare institutions and operates six high-throughput testing hubs 
-in the U.S.
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”
----
-Technology Platform:  
-Theranos’s diagnostics pipeline is powered by MicroVial Sensing (MVS), a next-gen detection framework combining nanophotonic arrays 
-and adaptive sample calibration. The system processes micro-samples through proprietary capillary modules, ensuring high sensitivity</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0.887</v>
+in the U.S.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1</v>
+        <v>0.91</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="26" ht="120" customHeight="1">
@@ -2007,10 +2110,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>- Approximately 325+ assays (over 300) can be run using an average sample of 1–2 µL capillary blood.</t>
+          <t>{
+  "answer": "- 325+ assays (over 300) per sample using 1–2 µL capillary blood.\n- The test menu includes 325+ assays across metabolic, hormonal, infectious, hematologic, and genomic panels.",
+  "citations": [
+    "Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels",
+    "The NanoDrop 3000 is capable of performing over 300 blood tests using just 1–2 microliters of capillary blood."
+  ]
+}</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>• Test menu: 325+ assays including metabolic, hormonal, infectious, hematologic, and genomic panels
+• The NanoDrop 3000 is capable of performing over 300 blood tests using just 1–2 microliters of capillary blood.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Flagship Product: NanoDrop 3000™  
 The NanoDrop 3000 is a compact, portable diagnostic device capable of performing over 300 blood tests using just 1–2 microliters 
@@ -2023,39 +2138,28 @@
 ---
 Q: What certifications does Theranos hold?  
 A: Theranos labs are CLIA-certified and CAP-accredited. NanoDrop 3000 is CE-marked and pending full FDA 510(k) clearance for expanded 
-panels.
----
-FAQs:
-Q: How accurate are Theranos test results?  
-A: Independent validation studies report sensitivity and specificity exceeding 94% for most core assays, with reproducibility between 
-92–97% across sample types and environments.
----
-Q: Where can I view the latest test menu?  
-A: Visit theranos.com/products/nanodrop3000/testmenu or access via the TheraCloud mobile app.
-Media Contacts:  
-press@theranos.com  
-investorrelations@theranos.com
-Company Motto: “One Drop Changes Everything™”</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>1</v>
+panels.</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.25</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.944</v>
+        <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2097,7 +2201,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.221</v>
+        <v>0.364</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
@@ -2127,7 +2231,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.863</v>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
@@ -2142,7 +2246,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.982</v>
+        <v>0.963</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -2157,7 +2261,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.981</v>
+        <v>0.982</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
